--- a/ksoft/docs/records/Stock_Group_Records.xlsx
+++ b/ksoft/docs/records/Stock_Group_Records.xlsx
@@ -2024,13 +2024,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7B4D978-1657-4E98-81EF-96ABE446E795}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC5D33AF-19C1-4751-BC66-AF8A8F9C67F1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4AB14D1-7323-43EA-B1C8-24B0D0F087AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FE57987-C7FC-4B3D-8893-6FD89C04783F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00EA5617-8F85-485D-8993-8196BDAF32FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{251CA369-0A5E-4268-A077-A9A5E983ECBF}"/>
 </file>
--- a/ksoft/docs/records/Stock_Group_Records.xlsx
+++ b/ksoft/docs/records/Stock_Group_Records.xlsx
@@ -2024,13 +2024,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC5D33AF-19C1-4751-BC66-AF8A8F9C67F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7B4D978-1657-4E98-81EF-96ABE446E795}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FE57987-C7FC-4B3D-8893-6FD89C04783F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4AB14D1-7323-43EA-B1C8-24B0D0F087AA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{251CA369-0A5E-4268-A077-A9A5E983ECBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00EA5617-8F85-485D-8993-8196BDAF32FD}"/>
 </file>